--- a/fine-tuning/final_model/results.xlsx
+++ b/fine-tuning/final_model/results.xlsx
@@ -8,7 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="test fine-tuned vs original" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="local test metrics (fine-tuned)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="local test box metrics (mAP)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="local photos and boxes per spli" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,6 +431,10 @@
   </sheetPr>
   <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
@@ -456,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fine-tuned from /content/rdd-roadscan/model/final_model/best.pt: 640 px, 20 epochs, on local photos</t>
+          <t>re-used saved fine-tuned weights</t>
         </is>
       </c>
     </row>
@@ -648,7 +655,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-24 15:07</t>
+          <t>2026-10-24 16:13</t>
         </is>
       </c>
     </row>
@@ -675,9 +682,643 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>original (merged) precision</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>original (merged) recall</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>original (merged) F1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fine-tuned precision</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fine-tuned recall</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fine-tuned F1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>precision change</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>recall change</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>F1 change</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Crack</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.169811320754717</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2022471910112359</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.4649122807017544</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4818181818181818</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2149122807017544</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3301886792452831</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2795709908069459</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Pothole</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1290322580645162</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4516129032258065</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Rut</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3448275862068966</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3448275862068966</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>macro (all classes)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.09169149288315126</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1104264830252507</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5498982964658021</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4395039322444041</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.482359575907963</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4110094075769133</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3478124393612528</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3719330928827123</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>macro (Crack + Pothole)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1375372393247269</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1656397245378761</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6074561403508771</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4868421052631579</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5312316715542522</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3991228070175438</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.349304865938431</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3655919470163762</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FN</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>real_boxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Crack</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4649122807017544</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.4818181818181818</v>
+      </c>
+      <c r="F2" t="n">
+        <v>53</v>
+      </c>
+      <c r="G2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H2" t="n">
+        <v>53</v>
+      </c>
+      <c r="I2" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Pothole</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Rut</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3448275862068966</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I4" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>macro (all classes)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>0.5498982964658021</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4395039322444041</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.482359575907963</v>
+      </c>
+      <c r="F5" t="n">
+        <v>72</v>
+      </c>
+      <c r="G5" t="n">
+        <v>77</v>
+      </c>
+      <c r="H5" t="n">
+        <v>82</v>
+      </c>
+      <c r="I5" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>macro (Crack + Pothole)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>0.6074561403508771</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4868421052631579</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5312316715542522</v>
+      </c>
+      <c r="F6" t="n">
+        <v>62</v>
+      </c>
+      <c r="G6" t="n">
+        <v>64</v>
+      </c>
+      <c r="H6" t="n">
+        <v>63</v>
+      </c>
+      <c r="I6" t="n">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>mAP50</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mAP50-95</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AP50_Crack</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>AP50_Pothole</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AP50_Rut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>fine-tuned</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.4898977765707503</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2397150900286747</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5312667371351523</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5499571956739362</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3884693969031625</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>photos</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>no damage</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Crack</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Pothole</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Rut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>574</v>
+      </c>
+      <c r="C2" t="n">
+        <v>238</v>
+      </c>
+      <c r="D2" t="n">
+        <v>461</v>
+      </c>
+      <c r="E2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>val</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>123</v>
+      </c>
+      <c r="C3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D3" t="n">
+        <v>103</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>123</v>
+      </c>
+      <c r="C4" t="n">
+        <v>42</v>
+      </c>
+      <c r="D4" t="n">
+        <v>106</v>
+      </c>
+      <c r="E4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>